--- a/diseases/d058/2005-2009.xlsx
+++ b/diseases/d058/2005-2009.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1069,6 +1079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1217,6 +1232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1362,6 +1382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1510,6 +1535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1658,6 +1688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1803,6 +1838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1951,6 +1991,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2099,6 +2144,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2244,6 +2294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2392,6 +2447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2540,6 +2600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2685,6 +2750,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2833,6 +2903,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2981,6 +3056,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3126,6 +3206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3274,6 +3359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3422,6 +3512,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3567,6 +3662,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3715,6 +3815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3863,6 +3968,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4008,6 +4118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4156,6 +4271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4304,6 +4424,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4449,6 +4574,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4597,6 +4727,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4745,6 +4880,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4890,6 +5030,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5038,6 +5183,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5186,6 +5336,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5331,6 +5486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5479,6 +5639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5627,6 +5792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5772,6 +5942,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5920,6 +6095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6068,6 +6248,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6213,6 +6398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6361,6 +6551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6509,6 +6704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6654,6 +6854,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6802,6 +7007,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6950,6 +7160,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7095,6 +7310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7243,6 +7463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7391,6 +7616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7536,6 +7766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7684,6 +7919,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7832,6 +8072,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7977,6 +8222,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8125,6 +8375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8273,6 +8528,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8418,6 +8678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8566,6 +8831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8714,6 +8984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8859,6 +9134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9007,6 +9287,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9155,6 +9440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9300,6 +9590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9448,6 +9743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9596,6 +9896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9741,6 +10046,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9889,6 +10199,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10037,6 +10352,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10182,6 +10502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10330,6 +10655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10478,6 +10808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10623,6 +10958,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10771,6 +11111,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10919,6 +11264,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11064,6 +11414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11212,6 +11567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11360,6 +11720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11505,6 +11870,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11653,6 +12023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11801,6 +12176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11946,6 +12326,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12094,6 +12479,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12242,6 +12632,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12387,6 +12782,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12535,6 +12935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12683,6 +13088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12828,6 +13238,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12976,6 +13391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13124,6 +13544,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13269,6 +13694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13417,6 +13847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13565,6 +14000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13710,6 +14150,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13858,6 +14303,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14006,6 +14456,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14151,6 +14606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14299,6 +14759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14447,6 +14912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14592,6 +15062,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14740,6 +15215,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14888,6 +15368,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15033,6 +15518,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15181,6 +15671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15329,6 +15824,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15474,6 +15974,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15622,6 +16127,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15770,6 +16280,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15915,6 +16430,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16063,6 +16583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16211,6 +16736,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16356,6 +16886,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16504,6 +17039,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16652,6 +17192,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16797,6 +17342,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16945,6 +17495,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17093,6 +17648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17238,6 +17798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17386,6 +17951,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17534,6 +18104,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17679,6 +18254,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17827,6 +18407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17975,6 +18560,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18120,6 +18710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18268,6 +18863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18416,6 +19016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18561,6 +19166,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18709,6 +19319,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18857,6 +19472,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19002,6 +19622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19150,6 +19775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19298,6 +19928,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19443,6 +20078,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19591,6 +20231,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19739,6 +20384,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19884,6 +20534,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20032,6 +20687,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20180,6 +20840,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20325,6 +20990,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20473,6 +21143,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20621,6 +21296,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20766,6 +21446,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20914,6 +21599,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21062,6 +21752,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21207,6 +21902,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21355,6 +22055,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21503,6 +22208,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21648,6 +22358,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21796,6 +22511,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21944,6 +22664,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22089,6 +22814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22237,6 +22967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22385,6 +23120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22530,6 +23270,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22678,6 +23423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22826,6 +23576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22971,6 +23726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23119,6 +23879,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23267,6 +24032,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23412,6 +24182,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23560,6 +24335,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23708,6 +24488,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23853,6 +24638,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24001,6 +24791,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24149,6 +24944,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24294,6 +25094,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24442,6 +25247,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24590,6 +25400,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24735,6 +25550,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24883,6 +25703,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25031,6 +25856,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25176,6 +26006,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25324,6 +26159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25472,6 +26312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25617,6 +26462,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25765,6 +26615,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25913,6 +26768,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26058,6 +26918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26206,6 +27071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26354,6 +27224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26499,6 +27374,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26647,6 +27527,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26795,6 +27680,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26940,6 +27830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27086,6 +27981,11 @@
       <c r="S181" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">

--- a/diseases/d058/2005-2009.xlsx
+++ b/diseases/d058/2005-2009.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>0.0208979235906712</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,22 +918,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1074,11 +1044,6 @@
       <c r="R4" t="n">
         <v>0.05695526402784604</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1091,22 +1056,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1227,11 +1182,6 @@
       <c r="R5" t="n">
         <v>0.0434248545918744</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1244,22 +1194,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1377,11 +1317,6 @@
       <c r="R6" t="n">
         <v>0.004179584718134241</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1394,22 +1329,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1530,11 +1455,6 @@
       <c r="R7" t="n">
         <v>0.04381174155988157</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1547,22 +1467,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1683,11 +1593,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1700,22 +1605,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1833,11 +1728,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1850,22 +1740,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1986,11 +1866,6 @@
       <c r="R10" t="n">
         <v>0.0306682190919171</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2003,22 +1878,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2139,11 +2004,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2156,22 +2016,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2289,11 +2139,6 @@
       <c r="R12" t="n">
         <v>0.00626937707720136</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2306,22 +2151,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2442,11 +2277,6 @@
       <c r="R13" t="n">
         <v>0.06571761233982236</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2459,22 +2289,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2595,11 +2415,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2612,22 +2427,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2745,11 +2550,6 @@
       <c r="R15" t="n">
         <v>0.008359169436268481</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2762,22 +2562,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2898,11 +2688,6 @@
       <c r="R16" t="n">
         <v>0.1533410954595855</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2915,22 +2700,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3051,11 +2826,6 @@
       <c r="R17" t="n">
         <v>0.072374757653124</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3068,22 +2838,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3201,11 +2961,6 @@
       <c r="R18" t="n">
         <v>0.01880813123160408</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3218,22 +2973,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3354,11 +3099,6 @@
       <c r="R19" t="n">
         <v>0.3198257133871355</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3371,22 +3111,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3507,11 +3237,6 @@
       <c r="R20" t="n">
         <v>0.0578998061224992</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3524,22 +3249,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3657,11 +3372,6 @@
       <c r="R21" t="n">
         <v>0.01462854651346984</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3674,22 +3384,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3810,11 +3510,6 @@
       <c r="R22" t="n">
         <v>0.3198257133871355</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3827,22 +3522,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3963,11 +3648,6 @@
       <c r="R23" t="n">
         <v>0.1013246607143736</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3980,22 +3660,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4113,11 +3783,6 @@
       <c r="R24" t="n">
         <v>0.0104489617953356</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4130,22 +3795,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4266,11 +3921,6 @@
       <c r="R25" t="n">
         <v>0.2015340111754552</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4283,22 +3933,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4419,11 +4059,6 @@
       <c r="R26" t="n">
         <v>0.0289499030612496</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4436,22 +4071,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4569,11 +4194,6 @@
       <c r="R27" t="n">
         <v>0.05015501661761088</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4586,22 +4206,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4722,11 +4332,6 @@
       <c r="R28" t="n">
         <v>0.363637454947017</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4739,22 +4344,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4875,11 +4470,6 @@
       <c r="R29" t="n">
         <v>0.0868497091837488</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4892,22 +4482,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5025,11 +4605,6 @@
       <c r="R30" t="n">
         <v>4.511861703225912</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5042,22 +4617,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5178,11 +4743,6 @@
       <c r="R31" t="n">
         <v>0.3198257133871355</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5195,22 +4755,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5331,11 +4881,6 @@
       <c r="R32" t="n">
         <v>0.0289499030612496</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5348,22 +4893,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5481,11 +5016,6 @@
       <c r="R33" t="n">
         <v>8.708164760232689</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5498,22 +5028,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5634,11 +5154,6 @@
       <c r="R34" t="n">
         <v>0.2015340111754552</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5651,22 +5166,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5787,11 +5292,6 @@
       <c r="R35" t="n">
         <v>0.0144749515306248</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5804,22 +5304,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5937,11 +5427,6 @@
       <c r="R36" t="n">
         <v>0.8150190200361769</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5954,22 +5439,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6090,11 +5565,6 @@
       <c r="R37" t="n">
         <v>0.0613364381838342</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6107,22 +5577,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6243,11 +5703,6 @@
       <c r="R38" t="n">
         <v>0.01442774513099671</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6260,22 +5715,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6393,11 +5838,6 @@
       <c r="R39" t="n">
         <v>0.02291355543546769</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6410,22 +5850,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6546,11 +5976,6 @@
       <c r="R40" t="n">
         <v>0.09600851578078881</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6563,22 +5988,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6699,11 +6114,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6716,22 +6126,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6849,11 +6249,6 @@
       <c r="R42" t="n">
         <v>0.006249151482400281</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6866,22 +6261,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7002,11 +6387,6 @@
       <c r="R43" t="n">
         <v>0.03927621100123179</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7019,22 +6399,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7155,11 +6525,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7172,22 +6537,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7305,11 +6660,6 @@
       <c r="R45" t="n">
         <v>0.008332201976533707</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7322,22 +6672,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7458,11 +6798,6 @@
       <c r="R46" t="n">
         <v>0.01745609377832524</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7475,22 +6810,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7611,11 +6936,6 @@
       <c r="R47" t="n">
         <v>0.01442774513099671</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7628,22 +6948,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7761,11 +7071,6 @@
       <c r="R48" t="n">
         <v>0.02707965642373455</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7778,22 +7083,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7914,11 +7209,6 @@
       <c r="R49" t="n">
         <v>0.03054816411206917</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7931,22 +7221,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8067,11 +7347,6 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8084,22 +7359,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8217,11 +7482,6 @@
       <c r="R51" t="n">
         <v>0.01666440395306741</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8234,22 +7494,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8370,11 +7620,6 @@
       <c r="R52" t="n">
         <v>0.1309207033374393</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8387,22 +7632,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8523,11 +7758,6 @@
       <c r="R53" t="n">
         <v>0.07213872565498355</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8540,22 +7770,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8673,11 +7893,6 @@
       <c r="R54" t="n">
         <v>0.01874745444720084</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8690,22 +7905,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8826,11 +8031,6 @@
       <c r="R55" t="n">
         <v>0.2312932425628094</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8843,22 +8043,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8979,11 +8169,6 @@
       <c r="R56" t="n">
         <v>0.01442774513099671</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8996,22 +8181,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9129,11 +8304,6 @@
       <c r="R57" t="n">
         <v>0.01041525247066713</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9146,22 +8316,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9282,11 +8442,6 @@
       <c r="R58" t="n">
         <v>0.2749334770086225</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9299,22 +8454,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9435,11 +8580,6 @@
       <c r="R59" t="n">
         <v>0.08656647078598027</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9452,22 +8592,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9585,11 +8715,6 @@
       <c r="R60" t="n">
         <v>0.01041525247066713</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9602,22 +8727,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9738,11 +8853,6 @@
       <c r="R61" t="n">
         <v>0.2443853128965534</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9755,22 +8865,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9891,11 +8991,6 @@
       <c r="R62" t="n">
         <v>0.04328323539299014</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9908,22 +9003,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10041,11 +9126,6 @@
       <c r="R63" t="n">
         <v>0.06040846432986937</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10058,22 +9138,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10194,11 +9264,6 @@
       <c r="R64" t="n">
         <v>0.2836615238977852</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10211,22 +9276,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10347,11 +9402,6 @@
       <c r="R65" t="n">
         <v>0.01442774513099671</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10364,22 +9414,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10497,11 +9537,6 @@
       <c r="R66" t="n">
         <v>4.278585714950059</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10514,22 +9549,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10650,11 +9675,6 @@
       <c r="R67" t="n">
         <v>0.1571048440049272</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10667,22 +9687,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10803,11 +9813,6 @@
       <c r="R68" t="n">
         <v>0.02885549026199342</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10820,22 +9825,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10953,11 +9948,6 @@
       <c r="R69" t="n">
         <v>7.844768160906485</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10970,22 +9960,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11106,11 +10086,6 @@
       <c r="R70" t="n">
         <v>0.1091005861145328</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11123,22 +10098,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11259,11 +10224,6 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11276,22 +10236,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11409,11 +10359,6 @@
       <c r="R72" t="n">
         <v>1.193587933138454</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11426,22 +10371,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11562,11 +10497,6 @@
       <c r="R73" t="n">
         <v>0.1309207033374393</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11579,22 +10509,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11715,11 +10635,6 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11732,22 +10647,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11865,11 +10770,6 @@
       <c r="R75" t="n">
         <v>0.05189077693019498</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11882,22 +10782,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12018,11 +10908,6 @@
       <c r="R76" t="n">
         <v>0.1651676686548797</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12035,22 +10920,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12171,11 +11046,6 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12188,22 +11058,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12321,11 +11181,6 @@
       <c r="R78" t="n">
         <v>0.02075631077207799</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12338,22 +11193,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12474,11 +11319,6 @@
       <c r="R79" t="n">
         <v>0.03477214076944837</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12491,22 +11331,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12627,11 +11457,6 @@
       <c r="R80" t="n">
         <v>0.01434443425192699</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12644,22 +11469,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12777,11 +11592,6 @@
       <c r="R81" t="n">
         <v>0.01245378646324679</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12794,22 +11604,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12930,11 +11730,6 @@
       <c r="R82" t="n">
         <v>0.04346517596181045</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12947,22 +11742,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13083,11 +11868,6 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13100,22 +11880,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13233,11 +12003,6 @@
       <c r="R84" t="n">
         <v>0.02283194184928579</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13250,22 +12015,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13386,11 +12141,6 @@
       <c r="R85" t="n">
         <v>0.09127686951980195</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13403,22 +12153,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13539,11 +12279,6 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13556,22 +12291,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13689,11 +12414,6 @@
       <c r="R87" t="n">
         <v>0.02698320400370139</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13706,22 +12426,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13842,11 +12552,6 @@
       <c r="R88" t="n">
         <v>0.2390584677899575</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13859,22 +12564,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13995,11 +12690,6 @@
       <c r="R89" t="n">
         <v>0.05737773700770798</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14012,22 +12702,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14145,11 +12825,6 @@
       <c r="R90" t="n">
         <v>0.03528572831253259</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14162,22 +12837,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14298,11 +12963,6 @@
       <c r="R91" t="n">
         <v>0.2694840909632248</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14315,22 +12975,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14451,11 +13101,6 @@
       <c r="R92" t="n">
         <v>0.02868886850385399</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14468,22 +13113,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14601,11 +13236,6 @@
       <c r="R93" t="n">
         <v>0.02490757292649359</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14618,22 +13248,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14754,11 +13374,6 @@
       <c r="R94" t="n">
         <v>0.4563843475990098</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14771,22 +13386,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14907,11 +13512,6 @@
       <c r="R95" t="n">
         <v>0.02868886850385399</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14924,22 +13524,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15057,11 +13647,6 @@
       <c r="R96" t="n">
         <v>0.02283194184928579</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15074,22 +13659,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15210,11 +13785,6 @@
       <c r="R97" t="n">
         <v>0.1217024926930693</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15227,22 +13797,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15363,11 +13923,6 @@
       <c r="R98" t="n">
         <v>0.02868886850385399</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15380,22 +13935,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15513,11 +14058,6 @@
       <c r="R99" t="n">
         <v>0.05396640800740277</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15530,22 +14070,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15666,11 +14196,6 @@
       <c r="R100" t="n">
         <v>0.2173258798090523</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15683,22 +14208,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15819,11 +14334,6 @@
       <c r="R101" t="n">
         <v>0.04303330275578099</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15836,22 +14346,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15969,11 +14469,6 @@
       <c r="R102" t="n">
         <v>2.330933699704358</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15986,22 +14481,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -16122,11 +14607,6 @@
       <c r="R103" t="n">
         <v>0.2303654325975954</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16139,22 +14619,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16275,11 +14745,6 @@
       <c r="R104" t="n">
         <v>0.01434443425192699</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16292,22 +14757,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16425,11 +14880,6 @@
       <c r="R105" t="n">
         <v>9.078810331706913</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16442,22 +14892,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16578,11 +15018,6 @@
       <c r="R106" t="n">
         <v>0.2738306085594058</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16595,22 +15030,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16731,11 +15156,6 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16748,22 +15168,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16881,11 +15291,6 @@
       <c r="R108" t="n">
         <v>0.8177986444198728</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16898,22 +15303,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -17034,11 +15429,6 @@
       <c r="R109" t="n">
         <v>0.1869002566357849</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17051,22 +15441,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17187,11 +15567,6 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17204,22 +15579,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17337,11 +15702,6 @@
       <c r="R111" t="n">
         <v>0.02895164461161399</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17354,22 +15714,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17490,11 +15840,6 @@
       <c r="R112" t="n">
         <v>0.220910820510868</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17507,22 +15852,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -17643,11 +15978,6 @@
       <c r="R113" t="n">
         <v>0.02848723454971688</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17660,22 +15990,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -17793,11 +16113,6 @@
       <c r="R114" t="n">
         <v>0.02067974615115285</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17810,22 +16125,12 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17946,11 +16251,6 @@
       <c r="R115" t="n">
         <v>0.06497377073849059</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17963,22 +16263,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -18099,11 +16389,6 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18116,22 +16401,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18249,11 +16524,6 @@
       <c r="R117" t="n">
         <v>0.004135949230230571</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18266,22 +16536,12 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -18402,11 +16662,6 @@
       <c r="R118" t="n">
         <v>0.04764743187489309</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18419,22 +16674,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18555,11 +16800,6 @@
       <c r="R119" t="n">
         <v>0.01424361727485844</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18572,22 +16812,12 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18705,11 +16935,6 @@
       <c r="R120" t="n">
         <v>0.01654379692092229</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18722,22 +16947,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18858,11 +17073,6 @@
       <c r="R121" t="n">
         <v>0.06497377073849059</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18875,22 +17085,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -19011,11 +17211,6 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19028,22 +17223,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -19161,11 +17346,6 @@
       <c r="R123" t="n">
         <v>0.04549544153253628</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19178,22 +17358,12 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -19314,11 +17484,6 @@
       <c r="R124" t="n">
         <v>0.1039580331815849</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19331,22 +17496,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -19467,11 +17622,6 @@
       <c r="R125" t="n">
         <v>0.02848723454971688</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19484,22 +17634,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -19617,11 +17757,6 @@
       <c r="R126" t="n">
         <v>0.01654379692092229</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19634,22 +17769,12 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19770,11 +17895,6 @@
       <c r="R127" t="n">
         <v>0.2728898371016604</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19787,22 +17907,12 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19923,11 +18033,6 @@
       <c r="R128" t="n">
         <v>0.05697446909943376</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19940,22 +18045,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20073,11 +18168,6 @@
       <c r="R129" t="n">
         <v>0.02481569538138343</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20090,22 +18180,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -20226,11 +18306,6 @@
       <c r="R130" t="n">
         <v>0.4504848104535347</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20243,22 +18318,12 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -20379,11 +18444,6 @@
       <c r="R131" t="n">
         <v>0.02848723454971688</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20396,22 +18456,12 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -20529,11 +18579,6 @@
       <c r="R132" t="n">
         <v>0.01240784769069171</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20546,22 +18591,12 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -20682,11 +18717,6 @@
       <c r="R133" t="n">
         <v>0.2122476510790692</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20699,22 +18729,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -20835,11 +18855,6 @@
       <c r="R134" t="n">
         <v>0.05697446909943376</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20852,22 +18867,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -20985,11 +18990,6 @@
       <c r="R135" t="n">
         <v>0.07858303537438086</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21002,22 +19002,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21138,11 +19128,6 @@
       <c r="R136" t="n">
         <v>0.1732633886359749</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21155,22 +19140,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21291,11 +19266,6 @@
       <c r="R137" t="n">
         <v>0.04273085182457532</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21308,22 +19278,12 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -21441,11 +19401,6 @@
       <c r="R138" t="n">
         <v>6.276302956874892</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21458,22 +19413,12 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -21594,11 +19539,6 @@
       <c r="R139" t="n">
         <v>0.1689318039200755</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21611,22 +19551,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -21747,11 +19677,6 @@
       <c r="R140" t="n">
         <v>0.01424361727485844</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21764,22 +19689,12 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -21897,11 +19812,6 @@
       <c r="R141" t="n">
         <v>5.267131344698632</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21914,22 +19824,12 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22050,11 +19950,6 @@
       <c r="R142" t="n">
         <v>0.2079160663631699</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22067,22 +19962,12 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22203,11 +20088,6 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22220,22 +20100,12 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22353,11 +20223,6 @@
       <c r="R144" t="n">
         <v>0.7341309883659264</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22370,22 +20235,12 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -22506,11 +20361,6 @@
       <c r="R145" t="n">
         <v>0.2122476510790692</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22523,22 +20373,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -22659,11 +20499,6 @@
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22676,22 +20511,12 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -22809,11 +20634,6 @@
       <c r="R147" t="n">
         <v>0.08033503996199617</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22826,22 +20646,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -22962,11 +20772,6 @@
       <c r="R148" t="n">
         <v>0.1079244102610903</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22979,22 +20784,12 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -23115,11 +20910,6 @@
       <c r="R149" t="n">
         <v>0.01415535058450628</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23132,22 +20922,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -23265,11 +21045,6 @@
       <c r="R150" t="n">
         <v>0.03501783793215218</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23282,22 +21057,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -23418,11 +21183,6 @@
       <c r="R151" t="n">
         <v>0.08202255179842863</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23435,22 +21195,12 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -23571,11 +21321,6 @@
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23588,22 +21333,12 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -23721,11 +21456,6 @@
       <c r="R153" t="n">
         <v>0.02677834665399872</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23738,22 +21468,12 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -23874,11 +21594,6 @@
       <c r="R154" t="n">
         <v>0.04748674051487974</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23891,22 +21606,12 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -24027,11 +21732,6 @@
       <c r="R155" t="n">
         <v>0.02831070116901255</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24044,22 +21744,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -24177,11 +21867,6 @@
       <c r="R156" t="n">
         <v>0.03089809229307545</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24194,22 +21879,12 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -24330,11 +22005,6 @@
       <c r="R157" t="n">
         <v>0.06907162256709778</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24347,22 +22017,12 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -24483,11 +22143,6 @@
       <c r="R158" t="n">
         <v>0.01415535058450628</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24500,22 +22155,12 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -24633,11 +22278,6 @@
       <c r="R159" t="n">
         <v>0.02883821947353709</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24650,22 +22290,12 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -24786,11 +22416,6 @@
       <c r="R160" t="n">
         <v>0.1165583630819775</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24803,22 +22428,12 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -24939,11 +22554,6 @@
       <c r="R161" t="n">
         <v>0.01415535058450628</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24956,22 +22566,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -25089,11 +22689,6 @@
       <c r="R162" t="n">
         <v>0.04325732921030563</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25106,22 +22701,12 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -25242,11 +22827,6 @@
       <c r="R163" t="n">
         <v>0.2072148677012934</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25259,22 +22839,12 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -25395,11 +22965,6 @@
       <c r="R164" t="n">
         <v>0.04246605175351883</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25412,22 +22977,12 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -25545,11 +23100,6 @@
       <c r="R165" t="n">
         <v>0.02883821947353709</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25562,22 +23112,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -25698,11 +23238,6 @@
       <c r="R166" t="n">
         <v>0.3065053251414964</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25715,22 +23250,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -25851,11 +23376,6 @@
       <c r="R167" t="n">
         <v>0.07077675292253138</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25868,22 +23388,12 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -26001,11 +23511,6 @@
       <c r="R168" t="n">
         <v>0.02471847383446036</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26018,22 +23523,12 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -26154,11 +23649,6 @@
       <c r="R169" t="n">
         <v>0.133826268723752</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26171,22 +23661,12 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -26307,11 +23787,6 @@
       <c r="R170" t="n">
         <v>0.0566214023380251</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26324,22 +23799,12 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -26457,11 +23922,6 @@
       <c r="R171" t="n">
         <v>0.1050535137964565</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26474,22 +23934,12 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -26610,11 +24060,6 @@
       <c r="R172" t="n">
         <v>0.15541115077597</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26627,22 +24072,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -26763,11 +24198,6 @@
       <c r="R173" t="n">
         <v>0.02831070116901255</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26780,22 +24210,12 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -26913,11 +24333,6 @@
       <c r="R174" t="n">
         <v>3.582118833177213</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26930,22 +24345,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -27066,11 +24471,6 @@
       <c r="R175" t="n">
         <v>0.1122413866715339</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27083,22 +24483,12 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -27219,11 +24609,6 @@
       <c r="R176" t="n">
         <v>0.01415535058450628</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27236,22 +24621,12 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -27369,11 +24744,6 @@
       <c r="R177" t="n">
         <v>5.440124116400817</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27386,22 +24756,12 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -27522,11 +24882,6 @@
       <c r="R178" t="n">
         <v>0.09497348102975947</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27539,22 +24894,12 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -27675,11 +25020,6 @@
       <c r="R179" t="n">
         <v>0</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27692,22 +25032,12 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -27825,11 +25155,6 @@
       <c r="R180" t="n">
         <v>0.8630867113865741</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27842,22 +25167,12 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -27978,11 +25293,6 @@
       <c r="R181" t="n">
         <v>0.1597281271864137</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27995,22 +25305,12 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
         <v>0</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>

--- a/diseases/d058/2005-2009.xlsx
+++ b/diseases/d058/2005-2009.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>0.0208979235906712</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,12 +938,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1182,6 +1212,11 @@
       <c r="R5" t="n">
         <v>0.0434248545918744</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1194,12 +1229,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1317,6 +1362,11 @@
       <c r="R6" t="n">
         <v>0.004179584718134241</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1329,12 +1379,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1593,6 +1653,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1605,12 +1670,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1728,6 +1803,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1740,12 +1820,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2004,6 +2094,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2016,12 +2111,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2139,6 +2244,11 @@
       <c r="R12" t="n">
         <v>0.00626937707720136</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2151,12 +2261,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2415,6 +2535,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2427,12 +2552,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2550,6 +2685,11 @@
       <c r="R15" t="n">
         <v>0.008359169436268481</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2562,12 +2702,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2826,6 +2976,11 @@
       <c r="R17" t="n">
         <v>0.072374757653124</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2838,12 +2993,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2961,6 +3126,11 @@
       <c r="R18" t="n">
         <v>0.01880813123160408</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2973,12 +3143,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3237,6 +3417,11 @@
       <c r="R20" t="n">
         <v>0.0578998061224992</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3249,12 +3434,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3372,6 +3567,11 @@
       <c r="R21" t="n">
         <v>0.01462854651346984</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3384,12 +3584,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3648,6 +3858,11 @@
       <c r="R23" t="n">
         <v>0.1013246607143736</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3660,12 +3875,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3783,6 +4008,11 @@
       <c r="R24" t="n">
         <v>0.0104489617953356</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3795,12 +4025,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4059,6 +4299,11 @@
       <c r="R26" t="n">
         <v>0.0289499030612496</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4071,12 +4316,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4194,6 +4449,11 @@
       <c r="R27" t="n">
         <v>0.05015501661761088</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4206,12 +4466,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4470,6 +4740,11 @@
       <c r="R29" t="n">
         <v>0.0868497091837488</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4482,12 +4757,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4605,6 +4890,11 @@
       <c r="R30" t="n">
         <v>4.511861703225912</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4617,12 +4907,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4881,6 +5181,11 @@
       <c r="R32" t="n">
         <v>0.0289499030612496</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4893,12 +5198,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5016,6 +5331,11 @@
       <c r="R33" t="n">
         <v>8.708164760232689</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5028,12 +5348,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5292,6 +5622,11 @@
       <c r="R35" t="n">
         <v>0.0144749515306248</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5304,12 +5639,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5427,6 +5772,11 @@
       <c r="R36" t="n">
         <v>0.8150190200361769</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5439,12 +5789,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5703,6 +6063,11 @@
       <c r="R38" t="n">
         <v>0.01442774513099671</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5715,12 +6080,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5838,6 +6213,11 @@
       <c r="R39" t="n">
         <v>0.02291355543546769</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5850,12 +6230,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6114,6 +6504,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6126,12 +6521,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6249,6 +6654,11 @@
       <c r="R42" t="n">
         <v>0.006249151482400281</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6261,12 +6671,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6525,6 +6945,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6537,12 +6962,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6660,6 +7095,11 @@
       <c r="R45" t="n">
         <v>0.008332201976533707</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6672,12 +7112,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6936,6 +7386,11 @@
       <c r="R47" t="n">
         <v>0.01442774513099671</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6948,12 +7403,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7071,6 +7536,11 @@
       <c r="R48" t="n">
         <v>0.02707965642373455</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7083,12 +7553,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7347,6 +7827,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7359,12 +7844,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7482,6 +7977,11 @@
       <c r="R51" t="n">
         <v>0.01666440395306741</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7494,12 +7994,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7758,6 +8268,11 @@
       <c r="R53" t="n">
         <v>0.07213872565498355</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7770,12 +8285,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -7893,6 +8418,11 @@
       <c r="R54" t="n">
         <v>0.01874745444720084</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7905,12 +8435,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8169,6 +8709,11 @@
       <c r="R56" t="n">
         <v>0.01442774513099671</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8181,12 +8726,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8304,6 +8859,11 @@
       <c r="R57" t="n">
         <v>0.01041525247066713</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8316,12 +8876,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8580,6 +9150,11 @@
       <c r="R59" t="n">
         <v>0.08656647078598027</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8592,12 +9167,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8715,6 +9300,11 @@
       <c r="R60" t="n">
         <v>0.01041525247066713</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8727,12 +9317,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -8991,6 +9591,11 @@
       <c r="R62" t="n">
         <v>0.04328323539299014</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9003,12 +9608,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9126,6 +9741,11 @@
       <c r="R63" t="n">
         <v>0.06040846432986937</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9138,12 +9758,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9402,6 +10032,11 @@
       <c r="R65" t="n">
         <v>0.01442774513099671</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9414,12 +10049,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9537,6 +10182,11 @@
       <c r="R66" t="n">
         <v>4.278585714950059</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9549,12 +10199,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -9813,6 +10473,11 @@
       <c r="R68" t="n">
         <v>0.02885549026199342</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9825,12 +10490,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -9948,6 +10623,11 @@
       <c r="R69" t="n">
         <v>7.844768160906485</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9960,12 +10640,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10224,6 +10914,11 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10236,12 +10931,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10359,6 +11064,11 @@
       <c r="R72" t="n">
         <v>1.193587933138454</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10371,12 +11081,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10635,6 +11355,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10647,12 +11372,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -10770,6 +11505,11 @@
       <c r="R75" t="n">
         <v>0.05189077693019498</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10782,12 +11522,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11046,6 +11796,11 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11058,12 +11813,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11181,6 +11946,11 @@
       <c r="R78" t="n">
         <v>0.02075631077207799</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11193,12 +11963,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11457,6 +12237,11 @@
       <c r="R80" t="n">
         <v>0.01434443425192699</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11469,12 +12254,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -11592,6 +12387,11 @@
       <c r="R81" t="n">
         <v>0.01245378646324679</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11604,12 +12404,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -11868,6 +12678,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11880,12 +12695,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12003,6 +12828,11 @@
       <c r="R84" t="n">
         <v>0.02283194184928579</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12015,12 +12845,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12279,6 +13119,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12291,12 +13136,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12414,6 +13269,11 @@
       <c r="R87" t="n">
         <v>0.02698320400370139</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12426,12 +13286,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12690,6 +13560,11 @@
       <c r="R89" t="n">
         <v>0.05737773700770798</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12702,12 +13577,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -12825,6 +13710,11 @@
       <c r="R90" t="n">
         <v>0.03528572831253259</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12837,12 +13727,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13101,6 +14001,11 @@
       <c r="R92" t="n">
         <v>0.02868886850385399</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13113,12 +14018,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13236,6 +14151,11 @@
       <c r="R93" t="n">
         <v>0.02490757292649359</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13248,12 +14168,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13512,6 +14442,11 @@
       <c r="R95" t="n">
         <v>0.02868886850385399</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13524,12 +14459,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -13647,6 +14592,11 @@
       <c r="R96" t="n">
         <v>0.02283194184928579</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13659,12 +14609,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -13923,6 +14883,11 @@
       <c r="R98" t="n">
         <v>0.02868886850385399</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13935,12 +14900,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14058,6 +15033,11 @@
       <c r="R99" t="n">
         <v>0.05396640800740277</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14070,12 +15050,22 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -14334,6 +15324,11 @@
       <c r="R101" t="n">
         <v>0.04303330275578099</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14346,12 +15341,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -14469,6 +15474,11 @@
       <c r="R102" t="n">
         <v>2.330933699704358</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14481,12 +15491,22 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -14745,6 +15765,11 @@
       <c r="R104" t="n">
         <v>0.01434443425192699</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14757,12 +15782,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -14880,6 +15915,11 @@
       <c r="R105" t="n">
         <v>9.078810331706913</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14892,12 +15932,22 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15156,6 +16206,11 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15168,12 +16223,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15291,6 +16356,11 @@
       <c r="R108" t="n">
         <v>0.8177986444198728</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15303,12 +16373,22 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -15567,6 +16647,11 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15579,12 +16664,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -15702,6 +16797,11 @@
       <c r="R111" t="n">
         <v>0.02895164461161399</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15714,12 +16814,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -15978,6 +17088,11 @@
       <c r="R113" t="n">
         <v>0.02848723454971688</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15990,12 +17105,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -16113,6 +17238,11 @@
       <c r="R114" t="n">
         <v>0.02067974615115285</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16125,12 +17255,22 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -16389,6 +17529,11 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16401,12 +17546,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -16524,6 +17679,11 @@
       <c r="R117" t="n">
         <v>0.004135949230230571</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16536,12 +17696,22 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -16800,6 +17970,11 @@
       <c r="R119" t="n">
         <v>0.01424361727485844</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16812,12 +17987,22 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -16935,6 +18120,11 @@
       <c r="R120" t="n">
         <v>0.01654379692092229</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16947,12 +18137,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -17211,6 +18411,11 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17223,12 +18428,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -17346,6 +18561,11 @@
       <c r="R123" t="n">
         <v>0.04549544153253628</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17358,12 +18578,22 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -17622,6 +18852,11 @@
       <c r="R125" t="n">
         <v>0.02848723454971688</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17634,12 +18869,22 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -17757,6 +19002,11 @@
       <c r="R126" t="n">
         <v>0.01654379692092229</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17769,12 +19019,22 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -18033,6 +19293,11 @@
       <c r="R128" t="n">
         <v>0.05697446909943376</v>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18045,12 +19310,22 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -18168,6 +19443,11 @@
       <c r="R129" t="n">
         <v>0.02481569538138343</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18180,12 +19460,22 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -18444,6 +19734,11 @@
       <c r="R131" t="n">
         <v>0.02848723454971688</v>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18456,12 +19751,22 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -18579,6 +19884,11 @@
       <c r="R132" t="n">
         <v>0.01240784769069171</v>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18591,12 +19901,22 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -18855,6 +20175,11 @@
       <c r="R134" t="n">
         <v>0.05697446909943376</v>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18867,12 +20192,22 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -18990,6 +20325,11 @@
       <c r="R135" t="n">
         <v>0.07858303537438086</v>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19002,12 +20342,22 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -19266,6 +20616,11 @@
       <c r="R137" t="n">
         <v>0.04273085182457532</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19278,12 +20633,22 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -19401,6 +20766,11 @@
       <c r="R138" t="n">
         <v>6.276302956874892</v>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19413,12 +20783,22 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -19677,6 +21057,11 @@
       <c r="R140" t="n">
         <v>0.01424361727485844</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19689,12 +21074,22 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -19812,6 +21207,11 @@
       <c r="R141" t="n">
         <v>5.267131344698632</v>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19824,12 +21224,22 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -20088,6 +21498,11 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20100,12 +21515,22 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -20223,6 +21648,11 @@
       <c r="R144" t="n">
         <v>0.7341309883659264</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20235,12 +21665,22 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -20499,6 +21939,11 @@
       <c r="R146" t="n">
         <v>0</v>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20511,12 +21956,22 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -20634,6 +22089,11 @@
       <c r="R147" t="n">
         <v>0.08033503996199617</v>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20646,12 +22106,22 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -20910,6 +22380,11 @@
       <c r="R149" t="n">
         <v>0.01415535058450628</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20922,12 +22397,22 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -21045,6 +22530,11 @@
       <c r="R150" t="n">
         <v>0.03501783793215218</v>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21057,12 +22547,22 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -21321,6 +22821,11 @@
       <c r="R152" t="n">
         <v>0</v>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21333,12 +22838,22 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -21456,6 +22971,11 @@
       <c r="R153" t="n">
         <v>0.02677834665399872</v>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21468,12 +22988,22 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -21732,6 +23262,11 @@
       <c r="R155" t="n">
         <v>0.02831070116901255</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21744,12 +23279,22 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -21867,6 +23412,11 @@
       <c r="R156" t="n">
         <v>0.03089809229307545</v>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21879,12 +23429,22 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -22143,6 +23703,11 @@
       <c r="R158" t="n">
         <v>0.01415535058450628</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22155,12 +23720,22 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -22278,6 +23853,11 @@
       <c r="R159" t="n">
         <v>0.02883821947353709</v>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22290,12 +23870,22 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -22554,6 +24144,11 @@
       <c r="R161" t="n">
         <v>0.01415535058450628</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22566,12 +24161,22 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -22689,6 +24294,11 @@
       <c r="R162" t="n">
         <v>0.04325732921030563</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22701,12 +24311,22 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -22965,6 +24585,11 @@
       <c r="R164" t="n">
         <v>0.04246605175351883</v>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22977,12 +24602,22 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -23100,6 +24735,11 @@
       <c r="R165" t="n">
         <v>0.02883821947353709</v>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23112,12 +24752,22 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -23376,6 +25026,11 @@
       <c r="R167" t="n">
         <v>0.07077675292253138</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23388,12 +25043,22 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -23511,6 +25176,11 @@
       <c r="R168" t="n">
         <v>0.02471847383446036</v>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23523,12 +25193,22 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -23787,6 +25467,11 @@
       <c r="R170" t="n">
         <v>0.0566214023380251</v>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23799,12 +25484,22 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -23922,6 +25617,11 @@
       <c r="R171" t="n">
         <v>0.1050535137964565</v>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23934,12 +25634,22 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -24198,6 +25908,11 @@
       <c r="R173" t="n">
         <v>0.02831070116901255</v>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24210,12 +25925,22 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -24333,6 +26058,11 @@
       <c r="R174" t="n">
         <v>3.582118833177213</v>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24345,12 +26075,22 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -24609,6 +26349,11 @@
       <c r="R176" t="n">
         <v>0.01415535058450628</v>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24621,12 +26366,22 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -24744,6 +26499,11 @@
       <c r="R177" t="n">
         <v>5.440124116400817</v>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24756,12 +26516,22 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -25020,6 +26790,11 @@
       <c r="R179" t="n">
         <v>0</v>
       </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25032,12 +26807,22 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -25155,6 +26940,11 @@
       <c r="R180" t="n">
         <v>0.8630867113865741</v>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25167,12 +26957,22 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
